--- a/Samples/Delphi/VCL/Patterns/Plural/Plural.xlsx
+++ b/Samples/Delphi/VCL/Patterns/Plural/Plural.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Context</t>
   </si>
@@ -23,6 +23,15 @@
     <t>Finnish</t>
   </si>
   <si>
+    <t>Japanese</t>
+  </si>
+  <si>
+    <t>Polish</t>
+  </si>
+  <si>
+    <t>Hebrew</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.RCData.TFORM1.Caption</t>
   </si>
   <si>
@@ -32,6 +41,12 @@
     <t>Monikko-esimerkki</t>
   </si>
   <si>
+    <t>サンプル</t>
+  </si>
+  <si>
+    <t>Lm liczba mnoga próbki</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.RCData.TFORM1.LanguageButton.Caption</t>
   </si>
   <si>
@@ -41,6 +56,9 @@
     <t>&amp;Kieli...</t>
   </si>
   <si>
+    <t>&amp;Język...</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.RCData.TFORM1.ZeroCheckBox.Caption</t>
   </si>
   <si>
@@ -50,6 +68,9 @@
     <t>&amp;Käytä nolla-osaa</t>
   </si>
   <si>
+    <t>&amp;Zero części</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.RCData.TNTLANGUAGEDIALOG.Caption</t>
   </si>
   <si>
@@ -59,12 +80,18 @@
     <t>Valitse kieli</t>
   </si>
   <si>
+    <t>Wybierz język</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.RCData.TNTLANGUAGEDIALOG.OkButton.Caption</t>
   </si>
   <si>
     <t>OK</t>
   </si>
   <si>
+    <t>Ok</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.RCData.TNTLANGUAGEDIALOG.CancelButton.Caption</t>
   </si>
   <si>
@@ -74,13 +101,19 @@
     <t>Peru</t>
   </si>
   <si>
+    <t>キャンセル</t>
+  </si>
+  <si>
+    <t>Anuluj</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.String.NtPattern.SMale</t>
   </si>
   <si>
     <t>Male</t>
   </si>
   <si>
-    <t>Maskuliini</t>
+    <t>Mies</t>
   </si>
   <si>
     <t>Win32\Release\Plural.exe.String.NtPattern.SFemale</t>
@@ -89,7 +122,7 @@
     <t>Female</t>
   </si>
   <si>
-    <t>Feminiini</t>
+    <t>Nainen</t>
   </si>
   <si>
     <t>Win32\Release\Plural.exe.String.NtPattern.SNeutral</t>
@@ -98,7 +131,7 @@
     <t>Neutral</t>
   </si>
   <si>
-    <t>Neutri</t>
+    <t>Neutraali</t>
   </si>
   <si>
     <t>Win32\Release\Plural.exe.String.NtPattern.SZero</t>
@@ -125,7 +158,7 @@
     <t>Dual</t>
   </si>
   <si>
-    <t>Kaksikko</t>
+    <t>Duaali</t>
   </si>
   <si>
     <t>Win32\Release\Plural.exe.String.NtPattern.SFew</t>
@@ -134,7 +167,7 @@
     <t>Few</t>
   </si>
   <si>
-    <t>Muutama</t>
+    <t>Vähän</t>
   </si>
   <si>
     <t>Win32\Release\Plural.exe.String.NtPattern.SMany</t>
@@ -143,7 +176,7 @@
     <t>Many</t>
   </si>
   <si>
-    <t>Monta</t>
+    <t>Paljon</t>
   </si>
   <si>
     <t>Win32\Release\Plural.exe.String.NtPattern.SPlural</t>
@@ -155,6 +188,9 @@
     <t>Monikko</t>
   </si>
   <si>
+    <t>複数</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.String.Unit1.SMessagePlural</t>
   </si>
   <si>
@@ -164,6 +200,15 @@
     <t>{plural, one {{0} tiedosto} other {{0} tiedostoa}}</t>
   </si>
   <si>
+    <t>{plural, other {{0}ファイル}}</t>
+  </si>
+  <si>
+    <t>{plural, one {{0} plik} few {{0} pliki} other {{0} plików}}</t>
+  </si>
+  <si>
+    <t>{plural, one {{0} קבצים} other {{0} קבצים}}</t>
+  </si>
+  <si>
     <t>Win32\Release\Plural.exe.String.Unit1.SZeroMessagePlural</t>
   </si>
   <si>
@@ -171,6 +216,9 @@
   </si>
   <si>
     <t>{plural, zero {Ei tiedostoa} one {{0} tiedosto} other {{0} tiedostoa}}</t>
+  </si>
+  <si>
+    <t>{plural, zero {Żadnych plików} one {{0} plik} few {{0} pliki} other {{0} plików}}</t>
   </si>
 </sst>
 </file>
@@ -225,12 +273,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -469,11 +520,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.4285714285714" defaultRowHeight="12.75" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="11.4285714285714" customWidth="1" style="2"/>
-    <col min="4" max="16384" width="11.4285714285714" style="2"/>
+    <col min="1" max="6" width="42.8571428571429" customWidth="1" style="3"/>
+    <col min="7" max="16384" width="11.4285714285714" style="3"/>
   </cols>
   <sheetData>
     <row ht="12.75" customHeight="1" r="1">
@@ -486,193 +537,283 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row ht="12.75" customHeight="1" r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="4">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="7">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="8">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="9">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="10">
       <c r="A10" s="2" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>28</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="11">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="12">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="13">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="14">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="15">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
     </row>
     <row ht="12.75" customHeight="1" r="16">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="17">
+        <v>57</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row ht="25.5" customHeight="1" r="17">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row ht="12.75" customHeight="1" r="18">
+        <v>61</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row ht="25.5" customHeight="1" r="18">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F18" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480315" right="0.78740157480315" top="0.78740157480315" bottom="0.78740157480315" header="0.393700787401575" footer="0.393700787401575"/>
